--- a/artfynd/A 15823-2022 artfynd.xlsx
+++ b/artfynd/A 15823-2022 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 15823-2022 artfynd.xlsx
+++ b/artfynd/A 15823-2022 artfynd.xlsx
@@ -809,7 +809,7 @@
         <v>131027184</v>
       </c>
       <c r="B3" t="n">
-        <v>96336</v>
+        <v>96337</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 15823-2022 artfynd.xlsx
+++ b/artfynd/A 15823-2022 artfynd.xlsx
@@ -809,7 +809,7 @@
         <v>131027184</v>
       </c>
       <c r="B3" t="n">
-        <v>96337</v>
+        <v>96338</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 15823-2022 artfynd.xlsx
+++ b/artfynd/A 15823-2022 artfynd.xlsx
@@ -809,7 +809,7 @@
         <v>131027184</v>
       </c>
       <c r="B3" t="n">
-        <v>96338</v>
+        <v>96341</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 15823-2022 artfynd.xlsx
+++ b/artfynd/A 15823-2022 artfynd.xlsx
@@ -809,7 +809,7 @@
         <v>131027184</v>
       </c>
       <c r="B3" t="n">
-        <v>96341</v>
+        <v>96342</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 15823-2022 artfynd.xlsx
+++ b/artfynd/A 15823-2022 artfynd.xlsx
@@ -809,7 +809,7 @@
         <v>131027184</v>
       </c>
       <c r="B3" t="n">
-        <v>96342</v>
+        <v>96344</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 15823-2022 artfynd.xlsx
+++ b/artfynd/A 15823-2022 artfynd.xlsx
@@ -809,7 +809,7 @@
         <v>131027184</v>
       </c>
       <c r="B3" t="n">
-        <v>96344</v>
+        <v>96345</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 15823-2022 artfynd.xlsx
+++ b/artfynd/A 15823-2022 artfynd.xlsx
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>4643</v>
+        <v>131027184</v>
       </c>
       <c r="B2" t="n">
-        <v>57278</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96441</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,48 +686,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100084</v>
+        <v>2668</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Hasselmus</t>
+          <t>Trubbfjädermossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Muscardinus avellanarius</t>
+          <t>Homalia trichomanoides</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
+          <t>(Hedw.) Brid.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Ragelskärr, Omberg, Ög</t>
+          <t>V Ragelsbrunn, Ög</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>480520.363829232</v>
+        <v>480242</v>
       </c>
       <c r="R2" t="n">
-        <v>6465743.825383323</v>
+        <v>6465616</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -759,27 +740,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2007-09-15</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-09-02</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2007-09-15</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Lövrikt hygge intill våtmark. Två präktiga yngelbon efter kort letande i täta smågranar. Markant ädellövinslag av bok, ek och lönn.</t>
+          <t>2021-09-02</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -789,27 +755,27 @@
         <v>0</v>
       </c>
       <c r="AG2" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Boris Berglund</t>
+          <t>Tomas Fasth</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Boris Berglund</t>
+          <t>Tomas Fasth</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>131027184</v>
+        <v>4643</v>
       </c>
       <c r="B3" t="n">
-        <v>96345</v>
+        <v>56614</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -817,34 +783,48 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2668</v>
+        <v>100084</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Trubbfjädermossa</t>
+          <t>Hasselmus</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Homalia trichomanoides</t>
+          <t>Muscardinus avellanarius</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>V Ragelsbrunn, Ög</t>
+          <t>Ragelskärr, Omberg, Ög</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>480242</v>
+        <v>480520</v>
       </c>
       <c r="R3" t="n">
-        <v>6465616</v>
+        <v>6465744</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -871,12 +851,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2021-09-02</t>
+          <t>2007-09-15</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2021-09-02</t>
+          <t>2007-09-15</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Lövrikt hygge intill våtmark. Två präktiga yngelbon efter kort letande i täta smågranar. Markant ädellövinslag av bok, ek och lönn.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -886,17 +871,17 @@
         <v>0</v>
       </c>
       <c r="AG3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Tomas Fasth</t>
+          <t>Boris Berglund</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Tomas Fasth</t>
+          <t>Boris Berglund</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>

--- a/artfynd/A 15823-2022 artfynd.xlsx
+++ b/artfynd/A 15823-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AZ3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131027184</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -885,8 +895,17 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/4643</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>